--- a/data/trans_orig/P41B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41B-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8959</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>21995</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>24993</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26163</t>
+          <t>26193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>21127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45935</t>
+          <t>44251</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>16229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>743873</t>
+          <t>743677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>764847</t>
+          <t>764546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1038858</t>
+          <t>1038983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1062822</t>
+          <t>1063587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1790234</t>
+          <t>1789261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1822697</t>
+          <t>1821835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,47 +2108,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5958</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2164</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12140</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5958</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>13335</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19379</t>
+          <t>18766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26846</t>
+          <t>26184</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>18941</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17546</t>
+          <t>17760</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>40092</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27873</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51044</t>
+          <t>49478</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29948</t>
+          <t>28669</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56282</t>
+          <t>51835</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62108</t>
+          <t>63020</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>94888</t>
+          <t>95951</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>44605</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24976</t>
+          <t>24647</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48357</t>
+          <t>47975</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49629</t>
+          <t>52026</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84229</t>
+          <t>83445</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -2545,12 +2545,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>536768</t>
+          <t>539031</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>573579</t>
+          <t>575536</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>597405</t>
+          <t>599248</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>635691</t>
+          <t>636315</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1150977</t>
+          <t>1150098</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1200898</t>
+          <t>1200131</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>13184</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12194</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22074</t>
+          <t>22048</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17541</t>
+          <t>18095</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>34183</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25599</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22950</t>
+          <t>20914</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20449</t>
+          <t>20393</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40993</t>
+          <t>40573</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>142306</t>
+          <t>141111</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>164453</t>
+          <t>164348</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>144806</t>
+          <t>144797</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>166289</t>
+          <t>166390</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>295970</t>
+          <t>294788</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>324828</t>
+          <t>326177</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>13286</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>836</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>26292</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4150,82 +4150,82 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>14638</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>7938</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>23748</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>29800</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>19779</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>41247</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>14638</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>8399</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>23778</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>29800</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>43530</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>22727</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>46642</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>21171</t>
+          <t>21718</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>45816</t>
+          <t>45533</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>48188</t>
+          <t>48155</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>81971</t>
+          <t>81859</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4361,12 +4361,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>40393</t>
+          <t>40794</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>69968</t>
+          <t>69845</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>40546</t>
+          <t>41317</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>70534</t>
+          <t>70613</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>89007</t>
+          <t>90615</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>129837</t>
+          <t>128163</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>34509</t>
+          <t>36332</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>62126</t>
+          <t>64749</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>41576</t>
+          <t>40102</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>72610</t>
+          <t>71550</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>84602</t>
+          <t>84740</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>125506</t>
+          <t>125334</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1445506</t>
+          <t>1443602</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1493431</t>
+          <t>1491974</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1802771</t>
+          <t>1801501</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1850595</t>
+          <t>1853108</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4637,12 +4637,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3263250</t>
+          <t>3262473</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3332364</t>
+          <t>3328658</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28887</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26354</t>
+          <t>27455</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51122</t>
+          <t>51006</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25142</t>
+          <t>25745</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6593</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22508</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>17558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>40440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21950</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18339</t>
+          <t>17842</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34505</t>
+          <t>34983</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>687142</t>
+          <t>686397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>714942</t>
+          <t>714790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1034601</t>
+          <t>1035107</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1064357</t>
+          <t>1065269</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1732994</t>
+          <t>1731690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1772249</t>
+          <t>1772252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30850</t>
+          <t>31185</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55787</t>
+          <t>56307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54307</t>
+          <t>53684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87354</t>
+          <t>87046</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91832</t>
+          <t>91248</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135326</t>
+          <t>133643</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37615</t>
+          <t>38738</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19328</t>
+          <t>19789</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24918</t>
+          <t>26486</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51182</t>
+          <t>51131</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26688</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50399</t>
+          <t>49838</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38772</t>
+          <t>39086</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67583</t>
+          <t>67740</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>72731</t>
+          <t>71512</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>109810</t>
+          <t>108636</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>22815</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48535</t>
+          <t>49047</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36194</t>
+          <t>36048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63638</t>
+          <t>62403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>668937</t>
+          <t>666859</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>708116</t>
+          <t>710011</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>682108</t>
+          <t>682491</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>731174</t>
+          <t>731388</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1365349</t>
+          <t>1361494</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1430059</t>
+          <t>1428231</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25608</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12886</t>
+          <t>12421</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31229</t>
+          <t>31001</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>15353</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24440</t>
+          <t>26671</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>17708</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>22180</t>
+          <t>23798</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>34553</t>
+          <t>34813</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -7768,12 +7768,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10969</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>26881</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13980</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32591</t>
+          <t>33303</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -7881,12 +7881,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>111746</t>
+          <t>112682</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>132476</t>
+          <t>133085</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>111456</t>
+          <t>110918</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>137241</t>
+          <t>136766</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7931,12 +7931,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>232150</t>
+          <t>231154</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>264309</t>
+          <t>264149</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -8111,12 +8111,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20037</t>
+          <t>19282</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -8224,12 +8224,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14232</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9297</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>18043</t>
+          <t>18572</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>52137</t>
+          <t>51783</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>83779</t>
+          <t>83652</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>84396</t>
+          <t>86833</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>126816</t>
+          <t>127516</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8500,12 +8500,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>146757</t>
+          <t>145307</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>200803</t>
+          <t>200969</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>34782</t>
+          <t>34149</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>64912</t>
+          <t>64899</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>20026</t>
+          <t>19269</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>43116</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>62604</t>
+          <t>59897</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>101842</t>
+          <t>99265</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -8676,12 +8676,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>47523</t>
+          <t>46646</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>76536</t>
+          <t>78533</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>59987</t>
+          <t>59083</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>95916</t>
+          <t>96187</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8726,12 +8726,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>113636</t>
+          <t>113202</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>159645</t>
+          <t>161039</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>31654</t>
+          <t>30369</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>47329</t>
+          <t>46719</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>79165</t>
+          <t>77421</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>65446</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>101380</t>
+          <t>99480</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -8902,12 +8902,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1485925</t>
+          <t>1486177</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1541498</t>
+          <t>1543720</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1849914</t>
+          <t>1848980</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1915883</t>
+          <t>1914126</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8952,47 +8952,47 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
+          <t>88,48%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>3127</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>3399014</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>3354515</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>3442316</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>87,45%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>86,3%</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
           <t>88,56%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>3127</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>3399014</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>3357144</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>3437099</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>87,45%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>86,37%</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -9702,12 +9702,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9772,12 +9772,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -9815,12 +9815,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24029</t>
+          <t>24513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10076,12 +10076,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10091,12 +10091,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -10154,12 +10154,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>561799</t>
+          <t>563078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>578532</t>
+          <t>578693</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10169,12 +10169,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>831519</t>
+          <t>830236</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>850188</t>
+          <t>850821</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1400576</t>
+          <t>1399116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1426364</t>
+          <t>1424053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -10497,12 +10497,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10512,12 +10512,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10532,12 +10532,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10567,12 +10567,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15319</t>
+          <t>14554</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -10723,12 +10723,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34838</t>
+          <t>34028</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10758,12 +10758,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18338</t>
+          <t>19368</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39693</t>
+          <t>39965</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36858</t>
+          <t>37795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67005</t>
+          <t>66545</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -10836,12 +10836,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>9720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26260</t>
+          <t>26751</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10871,12 +10871,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>27015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10886,12 +10886,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>23177</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47542</t>
+          <t>47373</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10921,12 +10921,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -10949,12 +10949,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>30049</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53766</t>
+          <t>56031</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20159</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40756</t>
+          <t>41822</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10999,12 +10999,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55601</t>
+          <t>56764</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>88211</t>
+          <t>89223</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11034,12 +11034,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -11062,12 +11062,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>37944</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11132,12 +11132,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>24693</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47598</t>
+          <t>46560</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11147,12 +11147,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -11175,12 +11175,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>883292</t>
+          <t>882257</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>920122</t>
+          <t>921085</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11210,12 +11210,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>914653</t>
+          <t>912464</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>952851</t>
+          <t>951114</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11245,12 +11245,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1808508</t>
+          <t>1806338</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1861396</t>
+          <t>1861115</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -11744,12 +11744,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12890</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11779,12 +11779,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25800</t>
+          <t>25915</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11794,12 +11794,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11814,12 +11814,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14641</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33861</t>
+          <t>32730</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11829,12 +11829,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -11857,12 +11857,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>12476</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11927,12 +11927,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11942,12 +11942,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -11970,12 +11970,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19898</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11985,12 +11985,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12005,12 +12005,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24748</t>
+          <t>24822</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12020,12 +12020,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12040,12 +12040,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>38642</t>
+          <t>38840</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12055,12 +12055,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -12083,12 +12083,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12118,12 +12118,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21990</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12133,12 +12133,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>27469</t>
+          <t>27147</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12168,12 +12168,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -12196,12 +12196,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>188939</t>
+          <t>187616</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>208854</t>
+          <t>208953</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12211,12 +12211,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>170899</t>
+          <t>170693</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>196328</t>
+          <t>194073</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12246,12 +12246,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>366162</t>
+          <t>366862</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>399255</t>
+          <t>399271</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12554,77 +12554,77 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>5104</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>12394</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>5104</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>1092</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>11214</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>9381</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>4080</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>16909</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,24%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>9381</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>4505</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>16941</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -12657,7 +12657,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -12765,12 +12765,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>20657</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>44292</t>
+          <t>45070</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>35426</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>64270</t>
+          <t>62250</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12835,12 +12835,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>63149</t>
+          <t>60737</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>98142</t>
+          <t>97838</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -12878,12 +12878,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19224</t>
+          <t>19276</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>42737</t>
+          <t>41856</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12893,12 +12893,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12913,12 +12913,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>16063</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>39733</t>
+          <t>36484</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12928,12 +12928,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>40352</t>
+          <t>41381</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>70823</t>
+          <t>71974</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>41309</t>
+          <t>40284</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>72404</t>
+          <t>70426</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13026,12 +13026,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>38831</t>
+          <t>39132</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>66903</t>
+          <t>66824</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>88534</t>
+          <t>87729</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>128567</t>
+          <t>126963</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -13104,12 +13104,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>24944</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13119,12 +13119,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13139,12 +13139,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>33438</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>59931</t>
+          <t>60603</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>45255</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>76926</t>
+          <t>76923</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -13217,12 +13217,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1645714</t>
+          <t>1649523</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1694625</t>
+          <t>1696578</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13232,12 +13232,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13252,12 +13252,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1931576</t>
+          <t>1933030</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1985105</t>
+          <t>1985183</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13267,12 +13267,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3598608</t>
+          <t>3598064</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3666287</t>
+          <t>3668876</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -13673,32 +13673,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13708,32 +13708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>17159</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>25747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13743,32 +13743,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23996</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16463</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>39023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -14022,12 +14022,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -14047,32 +14047,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>281</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -14082,22 +14082,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>819</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -14125,32 +14125,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14160,32 +14160,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14195,32 +14195,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>26568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -14238,32 +14238,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11972</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14273,32 +14273,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14308,32 +14308,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16162</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>880</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -14396,12 +14396,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -14411,7 +14411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>880</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -14464,32 +14464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>287754</t>
+          <t>308080</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277298</t>
+          <t>296767</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>295095</t>
+          <t>317382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14499,32 +14499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>393640</t>
+          <t>425792</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>383972</t>
+          <t>415029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>400461</t>
+          <t>433756</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14534,32 +14534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>681392</t>
+          <t>733872</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>667475</t>
+          <t>717445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692503</t>
+          <t>746479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -14577,17 +14577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>305314</t>
+          <t>333974</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>305314</t>
+          <t>333974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>305314</t>
+          <t>333974</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14612,17 +14612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>418422</t>
+          <t>456649</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>418422</t>
+          <t>456649</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>418422</t>
+          <t>456649</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14647,17 +14647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>723735</t>
+          <t>790623</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>723735</t>
+          <t>790623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>723735</t>
+          <t>790623</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14694,32 +14694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>308501</t>
+          <t>70821</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79791</t>
+          <t>53968</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>674417</t>
+          <t>91870</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14729,32 +14729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62674</t>
+          <t>71234</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31292</t>
+          <t>57114</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87949</t>
+          <t>86991</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14764,32 +14764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>371175</t>
+          <t>142055</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128676</t>
+          <t>118547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>963271</t>
+          <t>167067</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>920</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -14930,92 +14930,92 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3861</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>4943</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>4927</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -15033,32 +15033,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>20982</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15068,32 +15068,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>20053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15103,32 +15103,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>23465</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33288</t>
+          <t>36055</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -15146,32 +15146,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25299</t>
+          <t>36148</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42666</t>
+          <t>52005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15181,32 +15181,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31839</t>
+          <t>36632</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14712</t>
+          <t>27048</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45842</t>
+          <t>49102</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15216,32 +15216,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>72780</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34294</t>
+          <t>56707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81914</t>
+          <t>92974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -15259,32 +15259,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>32742</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50036</t>
+          <t>46284</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15294,32 +15294,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29817</t>
+          <t>29519</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>39538</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15329,32 +15329,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>61548</t>
+          <t>62262</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36723</t>
+          <t>49147</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85693</t>
+          <t>80317</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -15372,32 +15372,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>22729</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15407,32 +15407,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>22202</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15442,32 +15442,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>22357</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>35262</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -15485,32 +15485,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>592311</t>
+          <t>637714</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>270082</t>
+          <t>612822</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>796594</t>
+          <t>662822</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15520,32 +15520,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>836529</t>
+          <t>687322</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>790843</t>
+          <t>665026</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>906435</t>
+          <t>707212</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15555,32 +15555,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1428840</t>
+          <t>1325036</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>888246</t>
+          <t>1290578</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1662647</t>
+          <t>1356030</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -15598,17 +15598,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>978834</t>
+          <t>799824</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>978834</t>
+          <t>799824</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>978834</t>
+          <t>799824</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15633,17 +15633,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>980512</t>
+          <t>849708</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>980512</t>
+          <t>849708</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>980512</t>
+          <t>849708</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15668,17 +15668,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1959346</t>
+          <t>1649532</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1959346</t>
+          <t>1649532</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1959346</t>
+          <t>1649532</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15715,32 +15715,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>31182</t>
+          <t>26520</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60083</t>
+          <t>38921</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15750,32 +15750,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26624</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>37841</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15785,32 +15785,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>57807</t>
+          <t>54261</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41090</t>
+          <t>40534</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85591</t>
+          <t>71472</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -15941,7 +15941,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>807</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -15951,12 +15951,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -16021,12 +16021,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -16054,32 +16054,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16089,32 +16089,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21479</t>
+          <t>22703</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16124,32 +16124,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>8783</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25216</t>
+          <t>28099</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -16167,32 +16167,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16202,32 +16202,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17597</t>
+          <t>19217</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16237,32 +16237,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>19833</t>
+          <t>24377</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12626</t>
+          <t>16733</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31096</t>
+          <t>36553</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -16280,32 +16280,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>22593</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16315,32 +16315,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>20472</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>27446</t>
+          <t>30608</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16350,32 +16350,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>29416</t>
+          <t>33526</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>23251</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>40380</t>
+          <t>45337</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -16403,12 +16403,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -16418,7 +16418,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16428,32 +16428,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16463,32 +16463,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -16506,67 +16506,67 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>200902</t>
+          <t>224335</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>175731</t>
+          <t>209618</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>215183</t>
+          <t>238228</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>74,1%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>84,21%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>212474</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>198588</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>225200</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>73,05%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>68,28%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>83,61%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>191536</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>177548</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>203460</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>72,44%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>67,15%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16576,32 +16576,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>392437</t>
+          <t>436808</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>367849</t>
+          <t>417217</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>413658</t>
+          <t>456361</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,54%</t>
         </is>
       </c>
     </row>
@@ -16619,17 +16619,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>257356</t>
+          <t>282887</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>257356</t>
+          <t>282887</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>257356</t>
+          <t>282887</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16654,17 +16654,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>264402</t>
+          <t>290842</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>264402</t>
+          <t>290842</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>264402</t>
+          <t>290842</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16689,17 +16689,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>521757</t>
+          <t>573728</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>521757</t>
+          <t>573728</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>521757</t>
+          <t>573728</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16736,32 +16736,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>346926</t>
+          <t>106810</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>110344</t>
+          <t>86775</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>849235</t>
+          <t>130845</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16771,32 +16771,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>106052</t>
+          <t>116135</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>69033</t>
+          <t>98240</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>128615</t>
+          <t>136974</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16806,32 +16806,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>452978</t>
+          <t>222945</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>213540</t>
+          <t>195348</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1242681</t>
+          <t>253681</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -16962,7 +16962,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -16972,12 +16972,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -16987,7 +16987,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17032,22 +17032,22 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -17075,32 +17075,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>15682</t>
+          <t>17338</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25735</t>
+          <t>27334</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17110,32 +17110,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>21271</t>
+          <t>24777</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>33878</t>
+          <t>37114</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17145,32 +17145,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>42115</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24773</t>
+          <t>29874</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>57121</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -17188,102 +17188,102 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>37839</t>
+          <t>56377</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>22793</t>
+          <t>42727</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>58394</t>
+          <t>74918</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>57702</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>45223</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>70983</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>114079</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>95272</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>137272</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
           <t>3,79%</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>46023</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>29074</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>59082</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>83862</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>59663</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>107804</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -17301,32 +17301,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>47591</t>
+          <t>52745</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>29016</t>
+          <t>38672</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>70140</t>
+          <t>70569</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17336,32 +17336,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>51120</t>
+          <t>52342</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>31856</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>67707</t>
+          <t>66053</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17371,32 +17371,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>98711</t>
+          <t>105087</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>69949</t>
+          <t>85689</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>124771</t>
+          <t>125744</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -17414,32 +17414,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17449,32 +17449,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26771</t>
+          <t>30987</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17484,32 +17484,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>27365</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>42455</t>
+          <t>45087</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -17527,102 +17527,102 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1080966</t>
+          <t>1170129</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>635637</t>
+          <t>1138971</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1297711</t>
+          <t>1198466</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
+          <t>84,6%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>2229</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>1325587</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>1296071</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>1352121</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>82,99%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>81,15%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>84,66%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>3682</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2495716</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2452879</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>2537097</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>82,81%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>81,39%</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
           <t>84,18%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>2229</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>1421704</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>1377412</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>1507700</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>85,47%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>82,81%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>90,64%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>3682</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>2502670</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>1823939</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>2740209</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>78,09%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>56,91%</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -17640,17 +17640,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1541503</t>
+          <t>1416685</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1541503</t>
+          <t>1416685</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1541503</t>
+          <t>1416685</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17675,17 +17675,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1663335</t>
+          <t>1597198</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1663335</t>
+          <t>1597198</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1663335</t>
+          <t>1597198</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17710,17 +17710,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>3204838</t>
+          <t>3013883</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3204838</t>
+          <t>3013883</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3204838</t>
+          <t>3013883</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
